--- a/artfynd/A 8998-2025 artfynd.xlsx
+++ b/artfynd/A 8998-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,62 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72164563</v>
+        <v>134471230</v>
       </c>
       <c r="B3" t="n">
-        <v>99141</v>
+        <v>111471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>219711</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Morrarö, lövskogen i norr, Srm</t>
+          <t>Morrarön, Morrarön, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615878</v>
+        <v>615894</v>
       </c>
       <c r="R3" t="n">
-        <v>6591696</v>
+        <v>6591626</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2007-11-07</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2007-11-07</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,57 +866,71 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Flodin</t>
+          <t>Karin Severin Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Karin Severin Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>71333871</v>
+        <v>72164563</v>
       </c>
       <c r="B4" t="n">
-        <v>106813</v>
+        <v>99141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Morrarö, Srm</t>
+          <t>Morrarö, lövskogen i norr, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615862</v>
+        <v>615878</v>
       </c>
       <c r="R4" t="n">
-        <v>6591688</v>
+        <v>6591696</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2007-11-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2007-11-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,39 +977,39 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Per Flodin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>71333869</v>
+        <v>71333871</v>
       </c>
       <c r="B5" t="n">
-        <v>106156</v>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1086,10 +1086,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>71333870</v>
+        <v>71333869</v>
       </c>
       <c r="B6" t="n">
-        <v>101326</v>
+        <v>106156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1097,21 +1097,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,6 +1180,103 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>71333870</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Morrarö, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>615862</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6591688</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Aspö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-05-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-05-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8998-2025 artfynd.xlsx
+++ b/artfynd/A 8998-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72164529</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471230</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72164563</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71333871</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71333869</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1277,8 +1307,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71333870</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>